--- a/monitor_xlsx/20260312.xlsx
+++ b/monitor_xlsx/20260312.xlsx
@@ -900,7 +900,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1022,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2273,6 +2272,59 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>德律</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>278</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9272</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>622</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1525</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-18</v>
+      </c>
+      <c r="J22" t="n">
+        <v>119</v>
+      </c>
+      <c r="K22" t="n">
+        <v>8268</v>
+      </c>
+      <c r="L22" t="n">
+        <v>36422</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-58819</v>
+      </c>
+      <c r="N22" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
